--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_nuble.xlsx
@@ -60,12 +60,12 @@
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -674,7 +674,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>16107</v>
+        <v>16204</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2020</v>
@@ -691,7 +691,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>16204</v>
+        <v>16107</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
